--- a/data/halte_garderie.xlsx
+++ b/data/halte_garderie.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
   <si>
     <t xml:space="preserve">cle</t>
   </si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Enfants accueillis en Halte Garderie</t>
   </si>
   <si>
-    <t xml:space="preserve">Sur l'année en cours</t>
+    <t xml:space="preserve">En 2025</t>
   </si>
   <si>
     <t xml:space="preserve">assistante_maternelle</t>
@@ -84,7 +84,7 @@
     <t xml:space="preserve">Nombre d’assistantes maternelles</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette année</t>
+    <t xml:space="preserve">Déc. 2021</t>
   </si>
   <si>
     <t xml:space="preserve">enfant_trois</t>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t xml:space="preserve">responsable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">progression</t>
   </si>
   <si>
     <t xml:space="preserve">Renouvellement / Suivi du Contrat Territorial Global</t>
@@ -738,8 +741,8 @@
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>12</v>
+      <c r="B3" s="5" t="n">
+        <v>137</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>16</v>
@@ -810,7 +813,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -832,25 +835,31 @@
       <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="G1" s="5" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -858,19 +867,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -878,19 +890,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -898,19 +910,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -934,7 +949,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>28</v>
@@ -942,34 +957,34 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -993,22 +1008,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" s="1" t="n">
         <f aca="false">SUMIF(A:A,"poste",C:C)</f>
@@ -1021,10 +1036,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>80000</v>
@@ -1036,10 +1051,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>20000</v>
@@ -1051,10 +1066,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>28000</v>
@@ -1066,10 +1081,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>22000</v>
@@ -1100,15 +1115,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>60</v>
@@ -1116,7 +1131,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>65</v>
@@ -1124,7 +1139,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>67</v>
@@ -1132,7 +1147,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>63</v>
@@ -1140,7 +1155,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>68</v>
@@ -1148,7 +1163,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>74</v>
@@ -1156,7 +1171,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>68</v>
@@ -1164,7 +1179,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>73</v>
@@ -1172,7 +1187,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>47</v>
@@ -1180,7 +1195,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>63</v>
@@ -1188,7 +1203,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B12" s="1" t="n">
         <v>53</v>
@@ -1196,7 +1211,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B13" s="1" t="n">
         <v>51</v>
